--- a/output/yearly_benthic_cover_iteration_100_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_100_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.26840201723093</v>
+        <v>45.20884438171871</v>
       </c>
       <c r="M2" t="n">
-        <v>100.012631080289</v>
+        <v>100.0060738346798</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.966356693625</v>
+        <v>87.97768606213199</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88155563839176</v>
+        <v>45.8547746518507</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22860992527768</v>
+        <v>2.228659338903784</v>
       </c>
       <c r="E3" t="n">
-        <v>5.676170179298684</v>
+        <v>5.661619339410556</v>
       </c>
       <c r="F3" t="n">
-        <v>0.74286997509256</v>
+        <v>0.7428864463012614</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95738753820607</v>
+        <v>33.94794810920755</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17201885425776</v>
+        <v>34.17277652985802</v>
       </c>
       <c r="I3" t="n">
-        <v>6.54636287716374</v>
+        <v>6.580756009067944</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6429373443285</v>
+        <v>4.643040289382884</v>
       </c>
       <c r="K3" t="n">
-        <v>12.03364330637502</v>
+        <v>12.02231393786801</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84980747280634</v>
+        <v>48.88668846156254</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7650064175731</v>
+        <v>106.7637770512812</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.93309165124496</v>
+        <v>87.0251967079915</v>
       </c>
       <c r="C4" t="n">
-        <v>42.48098964176773</v>
+        <v>42.54261776983098</v>
       </c>
       <c r="D4" t="n">
-        <v>2.17815834029696</v>
+        <v>2.182506078326219</v>
       </c>
       <c r="E4" t="n">
-        <v>6.458795159693943</v>
+        <v>6.460290780779519</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444271401434253</v>
+        <v>0.7444501840357743</v>
       </c>
       <c r="G4" t="n">
-        <v>33.18865542242607</v>
+        <v>33.24492074750741</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24364844659756</v>
+        <v>34.24470846564562</v>
       </c>
       <c r="I4" t="n">
-        <v>5.466737516190599</v>
+        <v>5.495506801473372</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652669625896408</v>
+        <v>4.65281365022359</v>
       </c>
       <c r="K4" t="n">
-        <v>13.06690834875503</v>
+        <v>12.9748032920085</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27025859622271</v>
+        <v>44.29978016013085</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81815658674547</v>
+        <v>99.81720122197034</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.7222433661384</v>
+        <v>85.81859615856473</v>
       </c>
       <c r="C5" t="n">
-        <v>42.11845687692474</v>
+        <v>42.18883207476013</v>
       </c>
       <c r="D5" t="n">
-        <v>2.118854290334741</v>
+        <v>2.123414798022456</v>
       </c>
       <c r="E5" t="n">
-        <v>7.043560026004653</v>
+        <v>7.050003558434961</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457482058235413</v>
+        <v>0.7457767617272679</v>
       </c>
       <c r="G5" t="n">
-        <v>32.28503806691183</v>
+        <v>32.34481561145486</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3044174678829</v>
+        <v>34.30573103945432</v>
       </c>
       <c r="I5" t="n">
-        <v>4.563699022783616</v>
+        <v>4.587749628675444</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660926286397133</v>
+        <v>4.661104760795425</v>
       </c>
       <c r="K5" t="n">
-        <v>14.27775663386161</v>
+        <v>14.18140384143527</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45193266931947</v>
+        <v>43.47711111709702</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8481461801058</v>
+        <v>99.84734703329241</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.20774489437838</v>
+        <v>84.33800388149328</v>
       </c>
       <c r="C6" t="n">
-        <v>41.31254920381247</v>
+        <v>41.42060590099525</v>
       </c>
       <c r="D6" t="n">
-        <v>2.044508795155868</v>
+        <v>2.05078997498563</v>
       </c>
       <c r="E6" t="n">
-        <v>7.431221206230297</v>
+        <v>7.447031750173138</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468725750993258</v>
+        <v>0.7469053602209302</v>
       </c>
       <c r="G6" t="n">
-        <v>31.15223381845446</v>
+        <v>31.23856142497733</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35613845456899</v>
+        <v>34.35764657016279</v>
       </c>
       <c r="I6" t="n">
-        <v>3.808816450498658</v>
+        <v>3.828910299592654</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667953594370786</v>
+        <v>4.668158501380814</v>
       </c>
       <c r="K6" t="n">
-        <v>15.79225510562163</v>
+        <v>15.66199611850671</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76842627326638</v>
+        <v>42.78996049081261</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87323058270047</v>
+        <v>99.87256251031457</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.5620754839572</v>
+        <v>82.66796570323912</v>
       </c>
       <c r="C7" t="n">
-        <v>40.25816926931024</v>
+        <v>40.34504342926851</v>
       </c>
       <c r="D7" t="n">
-        <v>1.964211337924508</v>
+        <v>1.969248903559283</v>
       </c>
       <c r="E7" t="n">
-        <v>7.669043320418039</v>
+        <v>7.683409903284142</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478308946415226</v>
+        <v>0.7478675486492594</v>
       </c>
       <c r="G7" t="n">
-        <v>29.92873936901728</v>
+        <v>29.99649090606509</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40022115351005</v>
+        <v>34.40190723786593</v>
       </c>
       <c r="I7" t="n">
-        <v>3.178086316936283</v>
+        <v>3.194869024757532</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673943091509516</v>
+        <v>4.674172179057871</v>
       </c>
       <c r="K7" t="n">
-        <v>17.43792451604282</v>
+        <v>17.33203429676088</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19810575768866</v>
+        <v>42.21656365453748</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89419954304171</v>
+        <v>99.89364138056688</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.35326672206952</v>
+        <v>87.43909393578737</v>
       </c>
       <c r="C8" t="n">
-        <v>42.49655139693791</v>
+        <v>42.61679831673133</v>
       </c>
       <c r="D8" t="n">
-        <v>1.968414684784735</v>
+        <v>1.97343237557906</v>
       </c>
       <c r="E8" t="n">
-        <v>9.457947285881575</v>
+        <v>9.492323035638536</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494312278553068</v>
+        <v>0.7494563183363309</v>
       </c>
       <c r="G8" t="n">
-        <v>30.41169940338538</v>
+        <v>30.49212170592664</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47383648134412</v>
+        <v>34.47499064347122</v>
       </c>
       <c r="I8" t="n">
-        <v>5.607992464722747</v>
+        <v>5.572667867233513</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683945174095667</v>
+        <v>4.684101989602068</v>
       </c>
       <c r="K8" t="n">
-        <v>12.64673327793048</v>
+        <v>12.56090606421266</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67018141932156</v>
+        <v>44.63693380608399</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81346609418995</v>
+        <v>99.81463818702797</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.22733686262556</v>
+        <v>85.31537923919177</v>
       </c>
       <c r="C9" t="n">
-        <v>41.24045058478562</v>
+        <v>41.35760038711186</v>
       </c>
       <c r="D9" t="n">
-        <v>1.871814324988678</v>
+        <v>1.876951852011362</v>
       </c>
       <c r="E9" t="n">
-        <v>9.774110648616873</v>
+        <v>9.803634691735651</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508035381241593</v>
+        <v>0.7508186045413373</v>
       </c>
       <c r="G9" t="n">
-        <v>28.91923893401134</v>
+        <v>29.00137091898136</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53696275371134</v>
+        <v>34.53765580890151</v>
       </c>
       <c r="I9" t="n">
-        <v>4.681884549897161</v>
+        <v>4.652331084637177</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692522113275996</v>
+        <v>4.692616278383358</v>
       </c>
       <c r="K9" t="n">
-        <v>14.77266313737445</v>
+        <v>14.68462076080824</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83110870937541</v>
+        <v>43.80298252243455</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84422243153548</v>
+        <v>99.84520367035465</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.92490151145886</v>
+        <v>83.09964752645655</v>
       </c>
       <c r="C10" t="n">
-        <v>39.66379383761562</v>
+        <v>39.86320144962301</v>
       </c>
       <c r="D10" t="n">
-        <v>1.768345466651485</v>
+        <v>1.77748842131125</v>
       </c>
       <c r="E10" t="n">
-        <v>9.885107276728842</v>
+        <v>9.931284015441975</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519828839948713</v>
+        <v>0.751988049727247</v>
       </c>
       <c r="G10" t="n">
-        <v>27.3206612350717</v>
+        <v>27.46453029969898</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5912126637641</v>
+        <v>34.59145028745336</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9076989602799</v>
+        <v>3.882981142028453</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699893024967946</v>
+        <v>4.699925310795294</v>
       </c>
       <c r="K10" t="n">
-        <v>17.07509848854116</v>
+        <v>16.90035247354344</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13105532523497</v>
+        <v>43.10721465781585</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86994765139175</v>
+        <v>99.87076858098229</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.5803392207048</v>
+        <v>80.80774993246757</v>
       </c>
       <c r="C11" t="n">
-        <v>37.92427053839841</v>
+        <v>38.17269612858331</v>
       </c>
       <c r="D11" t="n">
-        <v>1.664209069203736</v>
+        <v>1.675730310815666</v>
       </c>
       <c r="E11" t="n">
-        <v>9.846449565355822</v>
+        <v>9.902759084548858</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529972224287718</v>
+        <v>0.752993130072811</v>
       </c>
       <c r="G11" t="n">
-        <v>25.71177016114703</v>
+        <v>25.89223386421255</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63787223172351</v>
+        <v>34.6376839833493</v>
       </c>
       <c r="I11" t="n">
-        <v>3.26080833066611</v>
+        <v>3.240142496513313</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706232640179824</v>
+        <v>4.706207062955069</v>
       </c>
       <c r="K11" t="n">
-        <v>19.41966077929519</v>
+        <v>19.19225006753242</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54752148896529</v>
+        <v>42.5271932166057</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89145280665889</v>
+        <v>99.89213941272143</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.20261861162538</v>
+        <v>78.377329504225</v>
       </c>
       <c r="C12" t="n">
-        <v>36.05059545498177</v>
+        <v>36.24331575258971</v>
       </c>
       <c r="D12" t="n">
-        <v>1.559708074712628</v>
+        <v>1.568840908383159</v>
       </c>
       <c r="E12" t="n">
-        <v>9.681574810658976</v>
+        <v>9.721631357233099</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538703911336672</v>
+        <v>0.7538588176123813</v>
       </c>
       <c r="G12" t="n">
-        <v>24.0972461198544</v>
+        <v>24.24065222990932</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6780379921487</v>
+        <v>34.67750561016953</v>
       </c>
       <c r="I12" t="n">
-        <v>2.720491278531588</v>
+        <v>2.703222970840126</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71168994458542</v>
+        <v>4.711617610077383</v>
       </c>
       <c r="K12" t="n">
-        <v>21.79738138837462</v>
+        <v>21.62267049577501</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06144514745843</v>
+        <v>42.04400979339879</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90942199081482</v>
+        <v>99.90999604176351</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.68585535287215</v>
+        <v>75.97621880474483</v>
       </c>
       <c r="C13" t="n">
-        <v>33.95348214851361</v>
+        <v>34.25932024849671</v>
       </c>
       <c r="D13" t="n">
-        <v>1.450075570787017</v>
+        <v>1.464269471556908</v>
       </c>
       <c r="E13" t="n">
-        <v>9.379276699482384</v>
+        <v>9.449452942430543</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546238518981538</v>
+        <v>0.7546046155017359</v>
       </c>
       <c r="G13" t="n">
-        <v>22.40344105936697</v>
+        <v>22.62488620816559</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71269718731509</v>
+        <v>34.71181231307985</v>
       </c>
       <c r="I13" t="n">
-        <v>2.269341909659062</v>
+        <v>2.254914407124361</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716399074363462</v>
+        <v>4.716278846885849</v>
       </c>
       <c r="K13" t="n">
-        <v>24.31414464712785</v>
+        <v>24.02378119525517</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65680400217712</v>
+        <v>41.64180902928035</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92443079781859</v>
+        <v>99.92491047303223</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.86028533260861</v>
+        <v>83.05343437594213</v>
       </c>
       <c r="C14" t="n">
-        <v>38.49766844803899</v>
+        <v>38.75973431574668</v>
       </c>
       <c r="D14" t="n">
-        <v>1.451722090083131</v>
+        <v>1.465899687586228</v>
       </c>
       <c r="E14" t="n">
-        <v>11.88282656792684</v>
+        <v>11.92688503169508</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554807056777012</v>
+        <v>0.7554447399213768</v>
       </c>
       <c r="G14" t="n">
-        <v>24.45135208471632</v>
+        <v>24.65465725533473</v>
       </c>
       <c r="H14" t="n">
-        <v>36.77458502059348</v>
+        <v>36.75504010510653</v>
       </c>
       <c r="I14" t="n">
-        <v>2.822564453125501</v>
+        <v>2.773977931789583</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721754410485633</v>
+        <v>4.721529624508605</v>
       </c>
       <c r="K14" t="n">
-        <v>17.13971466739139</v>
+        <v>16.94656562405787</v>
       </c>
       <c r="L14" t="n">
-        <v>44.26863811300333</v>
+        <v>44.20133695980304</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90602122843372</v>
+        <v>99.9076368996076</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.10321059047868</v>
+        <v>82.35313410354881</v>
       </c>
       <c r="C15" t="n">
-        <v>38.17632954698594</v>
+        <v>38.48786115489263</v>
       </c>
       <c r="D15" t="n">
-        <v>1.423995369495369</v>
+        <v>1.440265980752093</v>
       </c>
       <c r="E15" t="n">
-        <v>12.04827172950224</v>
+        <v>12.10395904510246</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562028425694657</v>
+        <v>0.7561522450872492</v>
       </c>
       <c r="G15" t="n">
-        <v>23.98435098865454</v>
+        <v>24.22352935379326</v>
       </c>
       <c r="H15" t="n">
-        <v>36.80973652654608</v>
+        <v>36.78946271654588</v>
       </c>
       <c r="I15" t="n">
-        <v>2.354385367651833</v>
+        <v>2.313813230472557</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726267766059161</v>
+        <v>4.725951531795308</v>
       </c>
       <c r="K15" t="n">
-        <v>17.89678940952131</v>
+        <v>17.6468658964512</v>
       </c>
       <c r="L15" t="n">
-        <v>43.84847647535037</v>
+        <v>43.78821800610645</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92159543185761</v>
+        <v>99.92294505745028</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.61457833498345</v>
+        <v>80.03337227066103</v>
       </c>
       <c r="C16" t="n">
-        <v>36.05118664245579</v>
+        <v>36.52550774052407</v>
       </c>
       <c r="D16" t="n">
-        <v>1.33047748804974</v>
+        <v>1.352888781227204</v>
       </c>
       <c r="E16" t="n">
-        <v>11.58429379042895</v>
+        <v>11.69126449372414</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568245379700309</v>
+        <v>0.756759978114379</v>
       </c>
       <c r="G16" t="n">
-        <v>22.40922950978188</v>
+        <v>22.75395068858163</v>
       </c>
       <c r="H16" t="n">
-        <v>36.83999883528961</v>
+        <v>36.81903106298466</v>
       </c>
       <c r="I16" t="n">
-        <v>1.963600811150544</v>
+        <v>1.929727402814156</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730153362312693</v>
+        <v>4.729749863214868</v>
       </c>
       <c r="K16" t="n">
-        <v>20.38542166501655</v>
+        <v>19.96662772933895</v>
       </c>
       <c r="L16" t="n">
-        <v>43.49799209898177</v>
+        <v>43.44359194040165</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93460040645411</v>
+        <v>99.93572741026468</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.39100171843286</v>
+        <v>81.78032358802898</v>
       </c>
       <c r="C17" t="n">
-        <v>37.34939626217707</v>
+        <v>37.80920673940051</v>
       </c>
       <c r="D17" t="n">
-        <v>1.331532067244583</v>
+        <v>1.353931596290239</v>
       </c>
       <c r="E17" t="n">
-        <v>12.38954690285212</v>
+        <v>12.48552297091942</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574244214096669</v>
+        <v>0.7573432933988502</v>
       </c>
       <c r="G17" t="n">
-        <v>22.90049720189149</v>
+        <v>23.2415524498352</v>
       </c>
       <c r="H17" t="n">
-        <v>37.34270481871413</v>
+        <v>37.31747427542087</v>
       </c>
       <c r="I17" t="n">
-        <v>1.935393672510454</v>
+        <v>1.891103418421558</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733902633810418</v>
+        <v>4.733395583742814</v>
       </c>
       <c r="K17" t="n">
-        <v>18.60899828156716</v>
+        <v>18.21967641197105</v>
       </c>
       <c r="L17" t="n">
-        <v>43.9771434285126</v>
+        <v>43.90812861973185</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93553797225682</v>
+        <v>99.93701177110341</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.98401160202275</v>
+        <v>79.57338420131325</v>
       </c>
       <c r="C18" t="n">
-        <v>35.24081515372535</v>
+        <v>35.89406417628656</v>
       </c>
       <c r="D18" t="n">
-        <v>1.244863099457778</v>
+        <v>1.274191209578005</v>
       </c>
       <c r="E18" t="n">
-        <v>11.85210328852067</v>
+        <v>12.01300945622007</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579403179766494</v>
+        <v>0.7578435865180317</v>
       </c>
       <c r="G18" t="n">
-        <v>21.40991165527395</v>
+        <v>21.87273117022216</v>
       </c>
       <c r="H18" t="n">
-        <v>37.36813966432151</v>
+        <v>37.34212581161054</v>
       </c>
       <c r="I18" t="n">
-        <v>1.613926589118126</v>
+        <v>1.57696055142673</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737126987354059</v>
+        <v>4.736522415737698</v>
       </c>
       <c r="K18" t="n">
-        <v>21.01598839797724</v>
+        <v>20.42661579868675</v>
       </c>
       <c r="L18" t="n">
-        <v>43.68943551294992</v>
+        <v>43.62678937451498</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94623906465252</v>
+        <v>99.9474693494883</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.99345762086884</v>
+        <v>78.69611408775239</v>
       </c>
       <c r="C19" t="n">
-        <v>34.49075312850813</v>
+        <v>35.25952760778667</v>
       </c>
       <c r="D19" t="n">
-        <v>1.209505910671699</v>
+        <v>1.243090997677274</v>
       </c>
       <c r="E19" t="n">
-        <v>11.74099781002663</v>
+        <v>11.93894253211049</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583786454851754</v>
+        <v>0.7582656584069366</v>
       </c>
       <c r="G19" t="n">
-        <v>20.8018172482516</v>
+        <v>21.33886579026326</v>
       </c>
       <c r="H19" t="n">
-        <v>37.38975018320912</v>
+        <v>37.36292306035345</v>
       </c>
       <c r="I19" t="n">
-        <v>1.353141288942285</v>
+        <v>1.314865683897628</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739866534282346</v>
+        <v>4.739160365043354</v>
       </c>
       <c r="K19" t="n">
-        <v>22.00654237913114</v>
+        <v>21.30388591224762</v>
       </c>
       <c r="L19" t="n">
-        <v>43.45762585233861</v>
+        <v>43.39278202020385</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95492135997789</v>
+        <v>99.95619554023813</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.37483215185429</v>
+        <v>76.2959176654557</v>
       </c>
       <c r="C20" t="n">
-        <v>32.08001043555142</v>
+        <v>33.06158879003594</v>
       </c>
       <c r="D20" t="n">
-        <v>1.116224756461927</v>
+        <v>1.157214359063181</v>
       </c>
       <c r="E20" t="n">
-        <v>11.02352271845197</v>
+        <v>11.2968705043634</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587570157570054</v>
+        <v>0.7586288258681672</v>
       </c>
       <c r="G20" t="n">
-        <v>19.19751130360346</v>
+        <v>19.86470977969837</v>
       </c>
       <c r="H20" t="n">
-        <v>37.40840467727313</v>
+        <v>37.38081784137319</v>
       </c>
       <c r="I20" t="n">
-        <v>1.128180331825533</v>
+        <v>1.096246193413345</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742231348481283</v>
+        <v>4.741430161676045</v>
       </c>
       <c r="K20" t="n">
-        <v>24.6251678481457</v>
+        <v>23.7040823345443</v>
       </c>
       <c r="L20" t="n">
-        <v>43.25723445827671</v>
+        <v>43.19780482864482</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96241274197382</v>
+        <v>99.96347595322507</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.39694129204354</v>
+        <v>81.94774102403414</v>
       </c>
       <c r="C21" t="n">
-        <v>35.89167290983551</v>
+        <v>36.61586570678621</v>
       </c>
       <c r="D21" t="n">
-        <v>1.116926167483028</v>
+        <v>1.157928501561042</v>
       </c>
       <c r="E21" t="n">
-        <v>13.05734087562049</v>
+        <v>13.20058439139974</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592338019330054</v>
+        <v>0.7590969924445767</v>
       </c>
       <c r="G21" t="n">
-        <v>20.98072560054436</v>
+        <v>21.52085227949804</v>
       </c>
       <c r="H21" t="n">
-        <v>39.20306229800922</v>
+        <v>39.04776991769253</v>
       </c>
       <c r="I21" t="n">
-        <v>1.53444128637214</v>
+        <v>1.517152738659615</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745211262081283</v>
+        <v>4.744356202778605</v>
       </c>
       <c r="K21" t="n">
-        <v>18.60305870795647</v>
+        <v>18.05225897596584</v>
       </c>
       <c r="L21" t="n">
-        <v>45.45415245944756</v>
+        <v>45.28133474899173</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94888407723954</v>
+        <v>99.94945943174379</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_100_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_100_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.20884438171871</v>
+        <v>45.50049326603655</v>
       </c>
       <c r="M2" t="n">
-        <v>100.0060738346798</v>
+        <v>99.868518869345</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.97768606213199</v>
+        <v>88.0008258555211</v>
       </c>
       <c r="C3" t="n">
-        <v>45.8547746518507</v>
+        <v>45.89293075361471</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228659338903784</v>
+        <v>2.228689785047848</v>
       </c>
       <c r="E3" t="n">
-        <v>5.661619339410556</v>
+        <v>5.684568680375384</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428864463012614</v>
+        <v>0.7428965950159494</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94794810920755</v>
+        <v>33.96097242976471</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17277652985802</v>
+        <v>34.17324337073367</v>
       </c>
       <c r="I3" t="n">
-        <v>6.580756009067944</v>
+        <v>6.567351275733849</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643040289382884</v>
+        <v>4.643103718849683</v>
       </c>
       <c r="K3" t="n">
-        <v>12.02231393786801</v>
+        <v>11.99917414447891</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88668846156254</v>
+        <v>48.87215655023198</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7637770512812</v>
+        <v>106.7642614483256</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.0251967079915</v>
+        <v>87.10843352797453</v>
       </c>
       <c r="C4" t="n">
-        <v>42.54261776983098</v>
+        <v>42.63686728428703</v>
       </c>
       <c r="D4" t="n">
-        <v>2.182506078326219</v>
+        <v>2.185771154132853</v>
       </c>
       <c r="E4" t="n">
-        <v>6.460290780779519</v>
+        <v>6.489145382812276</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444501840357743</v>
+        <v>0.744455667772059</v>
       </c>
       <c r="G4" t="n">
-        <v>33.24492074750741</v>
+        <v>33.30697452884281</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24470846564562</v>
+        <v>34.2449607175147</v>
       </c>
       <c r="I4" t="n">
-        <v>5.495506801473372</v>
+        <v>5.484278153324465</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65281365022359</v>
+        <v>4.652847923575368</v>
       </c>
       <c r="K4" t="n">
-        <v>12.9748032920085</v>
+        <v>12.89156647202547</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29978016013085</v>
+        <v>44.28913981936155</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81720122197034</v>
+        <v>99.81757357567405</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.81859615856473</v>
+        <v>86.05358660994456</v>
       </c>
       <c r="C5" t="n">
-        <v>42.18883207476013</v>
+        <v>42.43320511460285</v>
       </c>
       <c r="D5" t="n">
-        <v>2.123414798022456</v>
+        <v>2.134629896586235</v>
       </c>
       <c r="E5" t="n">
-        <v>7.050003558434961</v>
+        <v>7.100372703605533</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457767617272679</v>
+        <v>0.7457759183072759</v>
       </c>
       <c r="G5" t="n">
-        <v>32.34481561145486</v>
+        <v>32.52767951469758</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30573103945432</v>
+        <v>34.30569224213468</v>
       </c>
       <c r="I5" t="n">
-        <v>4.587749628675444</v>
+        <v>4.578336845192768</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661104760795425</v>
+        <v>4.661099489420473</v>
       </c>
       <c r="K5" t="n">
-        <v>14.18140384143527</v>
+        <v>13.94641339005546</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47711111709702</v>
+        <v>43.46804043552712</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84734703329241</v>
+        <v>99.84765894018543</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.33800388149328</v>
+        <v>84.91335458377216</v>
       </c>
       <c r="C6" t="n">
-        <v>41.42060590099525</v>
+        <v>42.00410612441213</v>
       </c>
       <c r="D6" t="n">
-        <v>2.05078997498563</v>
+        <v>2.079463280628617</v>
       </c>
       <c r="E6" t="n">
-        <v>7.447031750173138</v>
+        <v>7.553707109629061</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469053602209302</v>
+        <v>0.7468945536474475</v>
       </c>
       <c r="G6" t="n">
-        <v>31.23856142497733</v>
+        <v>31.68704573239671</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35764657016279</v>
+        <v>34.35714946778258</v>
       </c>
       <c r="I6" t="n">
-        <v>3.828910299592654</v>
+        <v>3.821003479391192</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668158501380814</v>
+        <v>4.668090960296547</v>
       </c>
       <c r="K6" t="n">
-        <v>15.66199611850671</v>
+        <v>15.08664541622784</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78996049081261</v>
+        <v>42.78207243588246</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87256251031457</v>
+        <v>99.87282397652243</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.66796570323912</v>
+        <v>83.57695890678966</v>
       </c>
       <c r="C7" t="n">
-        <v>40.34504342926851</v>
+        <v>41.26140992701256</v>
       </c>
       <c r="D7" t="n">
-        <v>1.969248903559283</v>
+        <v>2.014767074964433</v>
       </c>
       <c r="E7" t="n">
-        <v>7.683409903284142</v>
+        <v>7.850066120586104</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478675486492594</v>
+        <v>0.747844282310749</v>
       </c>
       <c r="G7" t="n">
-        <v>29.99649090606509</v>
+        <v>30.70119921772596</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40190723786593</v>
+        <v>34.40083698629444</v>
       </c>
       <c r="I7" t="n">
-        <v>3.194869024757532</v>
+        <v>3.188218460465793</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674172179057871</v>
+        <v>4.67402676444218</v>
       </c>
       <c r="K7" t="n">
-        <v>17.33203429676088</v>
+        <v>16.42304109321034</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21656365453748</v>
+        <v>42.20940999423845</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89364138056688</v>
+        <v>99.89386101446135</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.43909393578737</v>
+        <v>88.54521759844874</v>
       </c>
       <c r="C8" t="n">
-        <v>42.61679831673133</v>
+        <v>43.57416546830485</v>
       </c>
       <c r="D8" t="n">
-        <v>1.97343237557906</v>
+        <v>2.019104213377136</v>
       </c>
       <c r="E8" t="n">
-        <v>9.492323035638536</v>
+        <v>9.694749491997856</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494563183363309</v>
+        <v>0.7494541478896705</v>
       </c>
       <c r="G8" t="n">
-        <v>30.49212170592664</v>
+        <v>31.20465862519287</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47499064347122</v>
+        <v>34.47489080292483</v>
       </c>
       <c r="I8" t="n">
-        <v>5.572667867233513</v>
+        <v>5.718271892755942</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684101989602068</v>
+        <v>4.68408842431044</v>
       </c>
       <c r="K8" t="n">
-        <v>12.56090606421266</v>
+        <v>11.45478240155126</v>
       </c>
       <c r="L8" t="n">
-        <v>44.63693380608399</v>
+        <v>44.78085250500173</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81463818702797</v>
+        <v>99.80980037485783</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.31537923919177</v>
+        <v>86.71492386505102</v>
       </c>
       <c r="C9" t="n">
-        <v>41.35760038711186</v>
+        <v>42.63187717460924</v>
       </c>
       <c r="D9" t="n">
-        <v>1.876951852011362</v>
+        <v>1.936545210341289</v>
       </c>
       <c r="E9" t="n">
-        <v>9.803634691735651</v>
+        <v>10.09400348692014</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508186045413373</v>
+        <v>0.750829486938092</v>
       </c>
       <c r="G9" t="n">
-        <v>29.00137091898136</v>
+        <v>29.92873364365817</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53765580890151</v>
+        <v>34.53815639915223</v>
       </c>
       <c r="I9" t="n">
-        <v>4.652331084637177</v>
+        <v>4.773971344678033</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692616278383358</v>
+        <v>4.692684293363075</v>
       </c>
       <c r="K9" t="n">
-        <v>14.68462076080824</v>
+        <v>13.28507613494897</v>
       </c>
       <c r="L9" t="n">
-        <v>43.80298252243455</v>
+        <v>43.92420580453189</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84520367035465</v>
+        <v>99.84115911409012</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.09964752645655</v>
+        <v>84.69688943112632</v>
       </c>
       <c r="C10" t="n">
-        <v>39.86320144962301</v>
+        <v>41.35512896958271</v>
       </c>
       <c r="D10" t="n">
-        <v>1.77748842131125</v>
+        <v>1.846297698465986</v>
       </c>
       <c r="E10" t="n">
-        <v>9.931284015441975</v>
+        <v>10.28769078886011</v>
       </c>
       <c r="F10" t="n">
-        <v>0.751988049727247</v>
+        <v>0.7520069076636344</v>
       </c>
       <c r="G10" t="n">
-        <v>27.46453029969898</v>
+        <v>28.53398503128634</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59145028745336</v>
+        <v>34.59231775252718</v>
       </c>
       <c r="I10" t="n">
-        <v>3.882981142028453</v>
+        <v>3.984548079425367</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699925310795294</v>
+        <v>4.700043172897715</v>
       </c>
       <c r="K10" t="n">
-        <v>16.90035247354344</v>
+        <v>15.30311056887368</v>
       </c>
       <c r="L10" t="n">
-        <v>43.10721465781585</v>
+        <v>43.20915014641366</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87076858098229</v>
+        <v>99.86738968487006</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.80774993246757</v>
+        <v>82.6278435586035</v>
       </c>
       <c r="C11" t="n">
-        <v>38.17269612858331</v>
+        <v>39.90434400922901</v>
       </c>
       <c r="D11" t="n">
-        <v>1.675730310815666</v>
+        <v>1.754714936515819</v>
       </c>
       <c r="E11" t="n">
-        <v>9.902759084548858</v>
+        <v>10.33153744067033</v>
       </c>
       <c r="F11" t="n">
-        <v>0.752993130072811</v>
+        <v>0.7530155893120919</v>
       </c>
       <c r="G11" t="n">
-        <v>25.89223386421255</v>
+        <v>27.11860052380354</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6376839833493</v>
+        <v>34.63871710835622</v>
       </c>
       <c r="I11" t="n">
-        <v>3.240142496513313</v>
+        <v>3.324910526744921</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706207062955069</v>
+        <v>4.706347433200573</v>
       </c>
       <c r="K11" t="n">
-        <v>19.19225006753242</v>
+        <v>17.37215644139649</v>
       </c>
       <c r="L11" t="n">
-        <v>42.5271932166057</v>
+        <v>42.61281765827937</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89213941272143</v>
+        <v>99.88931810890487</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.377329504225</v>
+        <v>80.33772457521722</v>
       </c>
       <c r="C12" t="n">
-        <v>36.24331575258971</v>
+        <v>38.12954263563009</v>
       </c>
       <c r="D12" t="n">
-        <v>1.568840908383159</v>
+        <v>1.654116339165093</v>
       </c>
       <c r="E12" t="n">
-        <v>9.721631357233099</v>
+        <v>10.20155037833296</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538588176123813</v>
+        <v>0.7538822746859943</v>
       </c>
       <c r="G12" t="n">
-        <v>24.24065222990932</v>
+        <v>25.56387894593503</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67750561016953</v>
+        <v>34.67858463555573</v>
       </c>
       <c r="I12" t="n">
-        <v>2.703222970840126</v>
+        <v>2.773947784754955</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711617610077383</v>
+        <v>4.711764216787463</v>
       </c>
       <c r="K12" t="n">
-        <v>21.62267049577501</v>
+        <v>19.66227542478277</v>
       </c>
       <c r="L12" t="n">
-        <v>42.04400979339879</v>
+        <v>42.11582331384423</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90999604176351</v>
+        <v>99.90764137425708</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.97621880474483</v>
+        <v>77.94582563184881</v>
       </c>
       <c r="C13" t="n">
-        <v>34.25932024849671</v>
+        <v>36.16679952041105</v>
       </c>
       <c r="D13" t="n">
-        <v>1.464269471556908</v>
+        <v>1.549915568668228</v>
       </c>
       <c r="E13" t="n">
-        <v>9.449452942430543</v>
+        <v>9.944557255703788</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546046155017359</v>
+        <v>0.7546282698123068</v>
       </c>
       <c r="G13" t="n">
-        <v>22.62488620816559</v>
+        <v>23.95348684715463</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71181231307985</v>
+        <v>34.71290041136611</v>
       </c>
       <c r="I13" t="n">
-        <v>2.254914407124361</v>
+        <v>2.313910592816819</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716278846885849</v>
+        <v>4.716426686326916</v>
       </c>
       <c r="K13" t="n">
-        <v>24.02378119525517</v>
+        <v>22.05417436815121</v>
       </c>
       <c r="L13" t="n">
-        <v>41.64180902928035</v>
+        <v>41.70197200630566</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92491047303223</v>
+        <v>99.92294589486791</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.05343437594213</v>
+        <v>84.30109826336124</v>
       </c>
       <c r="C14" t="n">
-        <v>38.75973431574668</v>
+        <v>39.99870104146571</v>
       </c>
       <c r="D14" t="n">
-        <v>1.465899687586228</v>
+        <v>1.55183714216996</v>
       </c>
       <c r="E14" t="n">
-        <v>11.92688503169508</v>
+        <v>12.11858583482576</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554447399213768</v>
+        <v>0.7555638521861102</v>
       </c>
       <c r="G14" t="n">
-        <v>24.65465725533473</v>
+        <v>25.62230429678831</v>
       </c>
       <c r="H14" t="n">
-        <v>36.75504010510653</v>
+        <v>36.39505729988092</v>
       </c>
       <c r="I14" t="n">
-        <v>2.773977931789583</v>
+        <v>3.135475761346989</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721529624508605</v>
+        <v>4.722274076163187</v>
       </c>
       <c r="K14" t="n">
-        <v>16.94656562405787</v>
+        <v>15.69890173663877</v>
       </c>
       <c r="L14" t="n">
-        <v>44.20133695980304</v>
+        <v>44.19801078069766</v>
       </c>
       <c r="M14" t="n">
-        <v>99.9076368996076</v>
+        <v>99.89561355880213</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.35313410354881</v>
+        <v>83.58024019404097</v>
       </c>
       <c r="C15" t="n">
-        <v>38.48786115489263</v>
+        <v>39.76291580128141</v>
       </c>
       <c r="D15" t="n">
-        <v>1.440265980752093</v>
+        <v>1.524956500006728</v>
       </c>
       <c r="E15" t="n">
-        <v>12.10395904510246</v>
+        <v>12.34460690590259</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561522450872492</v>
+        <v>0.7563520247371232</v>
       </c>
       <c r="G15" t="n">
-        <v>24.22352935379326</v>
+        <v>25.17847937825574</v>
       </c>
       <c r="H15" t="n">
-        <v>36.78946271654588</v>
+        <v>36.43302309863283</v>
       </c>
       <c r="I15" t="n">
-        <v>2.313813230472557</v>
+        <v>2.615622131898936</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725951531795308</v>
+        <v>4.727200154607019</v>
       </c>
       <c r="K15" t="n">
-        <v>17.6468658964512</v>
+        <v>16.41975980595903</v>
       </c>
       <c r="L15" t="n">
-        <v>43.78821800610645</v>
+        <v>43.73022784383327</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92294505745028</v>
+        <v>99.91290345107372</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.03337227066103</v>
+        <v>81.23013253961493</v>
       </c>
       <c r="C16" t="n">
-        <v>36.52550774052407</v>
+        <v>37.81756800612879</v>
       </c>
       <c r="D16" t="n">
-        <v>1.352888781227204</v>
+        <v>1.434459996805535</v>
       </c>
       <c r="E16" t="n">
-        <v>11.69126449372414</v>
+        <v>11.97563880391036</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756759978114379</v>
+        <v>0.7570291483244693</v>
       </c>
       <c r="G16" t="n">
-        <v>22.75395068858163</v>
+        <v>23.68429620670596</v>
       </c>
       <c r="H16" t="n">
-        <v>36.81903106298466</v>
+        <v>36.46563973545216</v>
       </c>
       <c r="I16" t="n">
-        <v>1.929727402814156</v>
+        <v>2.181636471388534</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729749863214868</v>
+        <v>4.731432177027933</v>
       </c>
       <c r="K16" t="n">
-        <v>19.96662772933895</v>
+        <v>18.76986746038505</v>
       </c>
       <c r="L16" t="n">
-        <v>43.44359194040165</v>
+        <v>43.33990836315563</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93572741026468</v>
+        <v>99.92734382966947</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.78032358802898</v>
+        <v>82.77995873544714</v>
       </c>
       <c r="C17" t="n">
-        <v>37.80920673940051</v>
+        <v>38.93923260913024</v>
       </c>
       <c r="D17" t="n">
-        <v>1.353931596290239</v>
+        <v>1.435737825581697</v>
       </c>
       <c r="E17" t="n">
-        <v>12.48552297091942</v>
+        <v>12.71504821469787</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573432933988502</v>
+        <v>0.7577035161229978</v>
       </c>
       <c r="G17" t="n">
-        <v>23.2415524498352</v>
+        <v>24.06543044175243</v>
       </c>
       <c r="H17" t="n">
-        <v>37.31747427542087</v>
+        <v>36.85815969655263</v>
       </c>
       <c r="I17" t="n">
-        <v>1.891103418421558</v>
+        <v>2.212232064970773</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733395583742814</v>
+        <v>4.735646975768735</v>
       </c>
       <c r="K17" t="n">
-        <v>18.21967641197105</v>
+        <v>17.22004126455286</v>
       </c>
       <c r="L17" t="n">
-        <v>43.90812861973185</v>
+        <v>43.76705068817145</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93701177110341</v>
+        <v>99.92632456185456</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.57338420131325</v>
+        <v>80.52649432502717</v>
       </c>
       <c r="C18" t="n">
-        <v>35.89406417628656</v>
+        <v>37.0277100412032</v>
       </c>
       <c r="D18" t="n">
-        <v>1.274191209578005</v>
+        <v>1.352109660112898</v>
       </c>
       <c r="E18" t="n">
-        <v>12.01300945622007</v>
+        <v>12.28191731205259</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578435865180317</v>
+        <v>0.7582821718219219</v>
       </c>
       <c r="G18" t="n">
-        <v>21.87273117022216</v>
+        <v>22.66367883835969</v>
       </c>
       <c r="H18" t="n">
-        <v>37.34212581161054</v>
+        <v>36.88630815265245</v>
       </c>
       <c r="I18" t="n">
-        <v>1.57696055142673</v>
+        <v>1.844934616140615</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736522415737698</v>
+        <v>4.739263573887011</v>
       </c>
       <c r="K18" t="n">
-        <v>20.42661579868675</v>
+        <v>19.47350567497282</v>
       </c>
       <c r="L18" t="n">
-        <v>43.62678937451498</v>
+        <v>43.43733339313034</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9474693494883</v>
+        <v>99.93854910930636</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.69611408775239</v>
+        <v>79.63004086132536</v>
       </c>
       <c r="C19" t="n">
-        <v>35.25952760778667</v>
+        <v>36.41577543755368</v>
       </c>
       <c r="D19" t="n">
-        <v>1.243090997677274</v>
+        <v>1.319565515734798</v>
       </c>
       <c r="E19" t="n">
-        <v>11.93894253211049</v>
+        <v>12.24270780968883</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7582656584069366</v>
+        <v>0.7587705002168673</v>
       </c>
       <c r="G19" t="n">
-        <v>21.33886579026326</v>
+        <v>22.11818311562898</v>
       </c>
       <c r="H19" t="n">
-        <v>37.36292306035345</v>
+        <v>36.91006267613329</v>
       </c>
       <c r="I19" t="n">
-        <v>1.314865683897628</v>
+        <v>1.538435617567158</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739160365043354</v>
+        <v>4.74231562635542</v>
       </c>
       <c r="K19" t="n">
-        <v>21.30388591224762</v>
+        <v>20.36995913867467</v>
       </c>
       <c r="L19" t="n">
-        <v>43.39278202020385</v>
+        <v>43.16301723998997</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95619554023813</v>
+        <v>99.94875181621831</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.2959176654557</v>
+        <v>77.11267285052679</v>
       </c>
       <c r="C20" t="n">
-        <v>33.06158879003594</v>
+        <v>34.13553054402193</v>
       </c>
       <c r="D20" t="n">
-        <v>1.157214359063181</v>
+        <v>1.227146093753955</v>
       </c>
       <c r="E20" t="n">
-        <v>11.2968705043634</v>
+        <v>11.59904598587381</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7586288258681672</v>
+        <v>0.7591912290255134</v>
       </c>
       <c r="G20" t="n">
-        <v>19.86470977969837</v>
+        <v>20.56907496265138</v>
       </c>
       <c r="H20" t="n">
-        <v>37.38081784137319</v>
+        <v>36.93052884698777</v>
       </c>
       <c r="I20" t="n">
-        <v>1.096246193413345</v>
+        <v>1.282740550824891</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741430161676045</v>
+        <v>4.744945181409458</v>
       </c>
       <c r="K20" t="n">
-        <v>23.7040823345443</v>
+        <v>22.88732714947321</v>
       </c>
       <c r="L20" t="n">
-        <v>43.19780482864482</v>
+        <v>42.93440798379467</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96347595322507</v>
+        <v>99.95726567728981</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.94774102403414</v>
+        <v>82.68218648158121</v>
       </c>
       <c r="C21" t="n">
-        <v>36.61586570678621</v>
+        <v>37.49334059770237</v>
       </c>
       <c r="D21" t="n">
-        <v>1.157928501561042</v>
+        <v>1.2281070951551</v>
       </c>
       <c r="E21" t="n">
-        <v>13.20058439139974</v>
+        <v>13.44075292774687</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7590969924445767</v>
+        <v>0.7597857660888213</v>
       </c>
       <c r="G21" t="n">
-        <v>21.52085227949804</v>
+        <v>22.09405655547619</v>
       </c>
       <c r="H21" t="n">
-        <v>39.04776991769253</v>
+        <v>38.4683234049417</v>
       </c>
       <c r="I21" t="n">
-        <v>1.517152738659615</v>
+        <v>1.942499694117399</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744356202778605</v>
+        <v>4.748661038055132</v>
       </c>
       <c r="K21" t="n">
-        <v>18.05225897596584</v>
+        <v>17.3178135184188</v>
       </c>
       <c r="L21" t="n">
-        <v>45.28133474899173</v>
+        <v>45.12414656134258</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94945943174379</v>
+        <v>99.93530067746376</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_100_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_100_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.50049326603655</v>
+        <v>44.36047089947705</v>
       </c>
       <c r="M2" t="n">
-        <v>99.868518869345</v>
+        <v>93.3636300380135</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.0008258555211</v>
+        <v>81.32070426903425</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89293075361471</v>
+        <v>43.07625982458983</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228689785047848</v>
+        <v>2.171997168404884</v>
       </c>
       <c r="E3" t="n">
-        <v>5.684568680375384</v>
+        <v>4.132163712938962</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428965950159494</v>
+        <v>0.7375225424603821</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96097242976471</v>
+        <v>32.67045740809014</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17324337073367</v>
+        <v>33.92603695317757</v>
       </c>
       <c r="I3" t="n">
-        <v>6.567351275733849</v>
+        <v>3.073010593584925</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643103718849683</v>
+        <v>4.609515890377388</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99917414447891</v>
+        <v>18.67929573096573</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87215655023198</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7642614483256</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.10843352797453</v>
+        <v>88.19178782823289</v>
       </c>
       <c r="C4" t="n">
-        <v>42.63686728428703</v>
+        <v>42.62005843220201</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185771154132853</v>
+        <v>2.177601519033753</v>
       </c>
       <c r="E4" t="n">
-        <v>6.489145382812276</v>
+        <v>6.46570487024889</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744455667772059</v>
+        <v>0.7394255536543045</v>
       </c>
       <c r="G4" t="n">
-        <v>33.30697452884281</v>
+        <v>33.3472979729997</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2449607175147</v>
+        <v>34.013575468098</v>
       </c>
       <c r="I4" t="n">
-        <v>5.484278153324465</v>
+        <v>6.82677273385883</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652847923575368</v>
+        <v>4.621409710339403</v>
       </c>
       <c r="K4" t="n">
-        <v>12.89156647202547</v>
+        <v>11.8082121717671</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28913981936155</v>
+        <v>45.34475595885423</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81757357567405</v>
+        <v>99.77302656282336</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.05358660994456</v>
+        <v>86.64960803336301</v>
       </c>
       <c r="C5" t="n">
-        <v>42.43320511460285</v>
+        <v>42.13601300076937</v>
       </c>
       <c r="D5" t="n">
-        <v>2.134629896586235</v>
+        <v>2.102225940857224</v>
       </c>
       <c r="E5" t="n">
-        <v>7.100372703605533</v>
+        <v>7.192143211099433</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457759183072759</v>
+        <v>0.7410473349665693</v>
       </c>
       <c r="G5" t="n">
-        <v>32.52767951469758</v>
+        <v>32.19301338816199</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30569224213468</v>
+        <v>34.08817740846218</v>
       </c>
       <c r="I5" t="n">
-        <v>4.578336845192768</v>
+        <v>5.701454906274543</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661099489420473</v>
+        <v>4.631545843541057</v>
       </c>
       <c r="K5" t="n">
-        <v>13.94641339005546</v>
+        <v>13.350391966637</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46804043552712</v>
+        <v>44.32396245665311</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84765894018543</v>
+        <v>99.81036742405948</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.91335458377216</v>
+        <v>84.87632854713878</v>
       </c>
       <c r="C6" t="n">
-        <v>42.00410612441213</v>
+        <v>41.24701912584358</v>
       </c>
       <c r="D6" t="n">
-        <v>2.079463280628617</v>
+        <v>2.016133267764424</v>
       </c>
       <c r="E6" t="n">
-        <v>7.553707109629061</v>
+        <v>7.690951712688317</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468945536474475</v>
+        <v>0.7424326663725773</v>
       </c>
       <c r="G6" t="n">
-        <v>31.68704573239671</v>
+        <v>30.87460963163286</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35714946778258</v>
+        <v>34.15190265313855</v>
       </c>
       <c r="I6" t="n">
-        <v>3.821003479391192</v>
+        <v>4.760094450713442</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668090960296547</v>
+        <v>4.640204164828608</v>
       </c>
       <c r="K6" t="n">
-        <v>15.08664541622784</v>
+        <v>15.12367145286121</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78207243588246</v>
+        <v>43.47093567389869</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87282397652243</v>
+        <v>99.84162625260348</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.57695890678966</v>
+        <v>82.9419630240622</v>
       </c>
       <c r="C7" t="n">
-        <v>41.26140992701256</v>
+        <v>40.05088598464735</v>
       </c>
       <c r="D7" t="n">
-        <v>2.014767074964433</v>
+        <v>1.923098110000296</v>
       </c>
       <c r="E7" t="n">
-        <v>7.850066120586104</v>
+        <v>7.998229987496586</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747844282310749</v>
+        <v>0.7436181313556474</v>
       </c>
       <c r="G7" t="n">
-        <v>30.70119921772596</v>
+        <v>29.44989023241879</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40083698629444</v>
+        <v>34.20643404235977</v>
       </c>
       <c r="I7" t="n">
-        <v>3.188218460465793</v>
+        <v>3.973079199458318</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67402676444218</v>
+        <v>4.647613320972797</v>
       </c>
       <c r="K7" t="n">
-        <v>16.42304109321034</v>
+        <v>17.0580369759378</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20940999423845</v>
+        <v>42.75885219356169</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89386101446135</v>
+        <v>99.86777515414684</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.54521759844874</v>
+        <v>80.90105972145075</v>
       </c>
       <c r="C8" t="n">
-        <v>43.57416546830485</v>
+        <v>38.62574971414021</v>
       </c>
       <c r="D8" t="n">
-        <v>2.019104213377136</v>
+        <v>1.825900470740282</v>
       </c>
       <c r="E8" t="n">
-        <v>9.694749491997856</v>
+        <v>8.146552082085082</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494541478896705</v>
+        <v>0.7446339433589333</v>
       </c>
       <c r="G8" t="n">
-        <v>31.20465862519287</v>
+        <v>27.96142753144031</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47489080292483</v>
+        <v>34.25316139451093</v>
       </c>
       <c r="I8" t="n">
-        <v>5.718271892755942</v>
+        <v>3.315422153321881</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68408842431044</v>
+        <v>4.653962145993334</v>
       </c>
       <c r="K8" t="n">
-        <v>11.45478240155126</v>
+        <v>19.09894027854924</v>
       </c>
       <c r="L8" t="n">
-        <v>44.78085250500173</v>
+        <v>42.1649466962145</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80980037485783</v>
+        <v>99.88963668890395</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.71492386505102</v>
+        <v>78.6801349598904</v>
       </c>
       <c r="C9" t="n">
-        <v>42.63187717460924</v>
+        <v>36.91806456513673</v>
       </c>
       <c r="D9" t="n">
-        <v>1.936545210341289</v>
+        <v>1.721013445516241</v>
       </c>
       <c r="E9" t="n">
-        <v>10.09400348692014</v>
+        <v>8.13959646741373</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750829486938092</v>
+        <v>0.7455065584240341</v>
       </c>
       <c r="G9" t="n">
-        <v>29.92873364365817</v>
+        <v>26.35521131002638</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53815639915223</v>
+        <v>34.29330168750556</v>
       </c>
       <c r="I9" t="n">
-        <v>4.773971344678033</v>
+        <v>2.766089500854231</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692684293363075</v>
+        <v>4.659415990150213</v>
       </c>
       <c r="K9" t="n">
-        <v>13.28507613494897</v>
+        <v>21.31986504010961</v>
       </c>
       <c r="L9" t="n">
-        <v>43.92420580453189</v>
+        <v>41.66997533493916</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84115911409012</v>
+        <v>99.9079049401855</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.69688943112632</v>
+        <v>84.3476723744507</v>
       </c>
       <c r="C10" t="n">
-        <v>41.35512896958271</v>
+        <v>40.77306050772252</v>
       </c>
       <c r="D10" t="n">
-        <v>1.846297698465986</v>
+        <v>1.722960111659948</v>
       </c>
       <c r="E10" t="n">
-        <v>10.28769078886011</v>
+        <v>10.29534295719862</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520069076636344</v>
+        <v>0.7463498129500091</v>
       </c>
       <c r="G10" t="n">
-        <v>28.53398503128634</v>
+        <v>28.05452669411325</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59231775252718</v>
+        <v>36.00159597400821</v>
       </c>
       <c r="I10" t="n">
-        <v>3.984548079425367</v>
+        <v>2.862210493583106</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700043172897715</v>
+        <v>4.664686330937557</v>
       </c>
       <c r="K10" t="n">
-        <v>15.30311056887368</v>
+        <v>15.6523276255493</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20915014641366</v>
+        <v>43.47931264476673</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86738968487006</v>
+        <v>99.90470077803855</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.6278435586035</v>
+        <v>83.78920519288991</v>
       </c>
       <c r="C11" t="n">
-        <v>39.90434400922901</v>
+        <v>40.5626987611267</v>
       </c>
       <c r="D11" t="n">
-        <v>1.754714936515819</v>
+        <v>1.693036324834565</v>
       </c>
       <c r="E11" t="n">
-        <v>10.33153744067033</v>
+        <v>10.55947797125823</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530155893120919</v>
+        <v>0.7470760369994285</v>
       </c>
       <c r="G11" t="n">
-        <v>27.11860052380354</v>
+        <v>27.60257732966553</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63871710835622</v>
+        <v>36.0719189053189</v>
       </c>
       <c r="I11" t="n">
-        <v>3.324910526744921</v>
+        <v>2.445893393566824</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706347433200573</v>
+        <v>4.669225231246428</v>
       </c>
       <c r="K11" t="n">
-        <v>17.37215644139649</v>
+        <v>16.2107948071101</v>
       </c>
       <c r="L11" t="n">
-        <v>42.61281765827937</v>
+        <v>43.14505590614174</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88931810890487</v>
+        <v>99.91854947437852</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.33772457521722</v>
+        <v>81.51555604967062</v>
       </c>
       <c r="C12" t="n">
-        <v>38.12954263563009</v>
+        <v>38.66822593531165</v>
       </c>
       <c r="D12" t="n">
-        <v>1.654116339165093</v>
+        <v>1.597783882656983</v>
       </c>
       <c r="E12" t="n">
-        <v>10.20155037833296</v>
+        <v>10.30537869440274</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538822746859943</v>
+        <v>0.7476992284121318</v>
       </c>
       <c r="G12" t="n">
-        <v>25.56387894593503</v>
+        <v>26.04962015888356</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67858463555573</v>
+        <v>36.10200916251924</v>
       </c>
       <c r="I12" t="n">
-        <v>2.773947784754955</v>
+        <v>2.03994474522014</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711764216787463</v>
+        <v>4.673120177575823</v>
       </c>
       <c r="K12" t="n">
-        <v>19.66227542478277</v>
+        <v>18.48444395032937</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11582331384423</v>
+        <v>42.77938863120436</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90764137425708</v>
+        <v>99.93205851684537</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.94582563184881</v>
+        <v>82.7999667536597</v>
       </c>
       <c r="C13" t="n">
-        <v>36.16679952041105</v>
+        <v>39.71821381105264</v>
       </c>
       <c r="D13" t="n">
-        <v>1.549915568668228</v>
+        <v>1.599002044941722</v>
       </c>
       <c r="E13" t="n">
-        <v>9.944557255703788</v>
+        <v>10.98030775025856</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546282698123068</v>
+        <v>0.7482692798504186</v>
       </c>
       <c r="G13" t="n">
-        <v>23.95348684715463</v>
+        <v>26.42091619684716</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71290041136611</v>
+        <v>36.48096921642934</v>
       </c>
       <c r="I13" t="n">
-        <v>2.313910592816819</v>
+        <v>1.893819266267366</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716426686326916</v>
+        <v>4.676682999065116</v>
       </c>
       <c r="K13" t="n">
-        <v>22.05417436815121</v>
+        <v>17.20003324634031</v>
       </c>
       <c r="L13" t="n">
-        <v>41.70197200630566</v>
+        <v>43.01867372579429</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92294589486791</v>
+        <v>99.93692078318723</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.30109826336124</v>
+        <v>80.59294882712764</v>
       </c>
       <c r="C14" t="n">
-        <v>39.99870104146571</v>
+        <v>37.80450779901408</v>
       </c>
       <c r="D14" t="n">
-        <v>1.55183714216996</v>
+        <v>1.509500026799366</v>
       </c>
       <c r="E14" t="n">
-        <v>12.11858583482576</v>
+        <v>10.6289018468091</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555638521861102</v>
+        <v>0.7487580227622144</v>
       </c>
       <c r="G14" t="n">
-        <v>25.62230429678831</v>
+        <v>24.94204046415599</v>
       </c>
       <c r="H14" t="n">
-        <v>36.39505729988092</v>
+        <v>36.50479728955769</v>
       </c>
       <c r="I14" t="n">
-        <v>3.135475761346989</v>
+        <v>1.579213534779446</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722274076163187</v>
+        <v>4.679737642263839</v>
       </c>
       <c r="K14" t="n">
-        <v>15.69890173663877</v>
+        <v>19.40705117287235</v>
       </c>
       <c r="L14" t="n">
-        <v>44.19801078069766</v>
+        <v>42.73583493738393</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89561355880213</v>
+        <v>99.94739390927036</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.58024019404097</v>
+        <v>79.64211635808758</v>
       </c>
       <c r="C15" t="n">
-        <v>39.76291580128141</v>
+        <v>37.06703221553895</v>
       </c>
       <c r="D15" t="n">
-        <v>1.524956500006728</v>
+        <v>1.470170864271354</v>
       </c>
       <c r="E15" t="n">
-        <v>12.34460690590259</v>
+        <v>10.57638039270101</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563520247371232</v>
+        <v>0.7491799796107648</v>
       </c>
       <c r="G15" t="n">
-        <v>25.17847937825574</v>
+        <v>24.29218982104273</v>
       </c>
       <c r="H15" t="n">
-        <v>36.43302309863283</v>
+        <v>36.52536928845854</v>
       </c>
       <c r="I15" t="n">
-        <v>2.615622131898936</v>
+        <v>1.346451139435896</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727200154607019</v>
+        <v>4.682374872567278</v>
       </c>
       <c r="K15" t="n">
-        <v>16.41975980595903</v>
+        <v>20.35788364191243</v>
       </c>
       <c r="L15" t="n">
-        <v>43.73022784383327</v>
+        <v>42.53022771639613</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91290345107372</v>
+        <v>99.95514357384751</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.23013253961493</v>
+        <v>77.1186418765686</v>
       </c>
       <c r="C16" t="n">
-        <v>37.81756800612879</v>
+        <v>34.75145367880633</v>
       </c>
       <c r="D16" t="n">
-        <v>1.434459996805535</v>
+        <v>1.368741475771489</v>
       </c>
       <c r="E16" t="n">
-        <v>11.97563880391036</v>
+        <v>10.03379720155975</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570291483244693</v>
+        <v>0.7495434973137973</v>
       </c>
       <c r="G16" t="n">
-        <v>23.68429620670596</v>
+        <v>22.61623363203733</v>
       </c>
       <c r="H16" t="n">
-        <v>36.46563973545216</v>
+        <v>36.54309215707158</v>
       </c>
       <c r="I16" t="n">
-        <v>2.181636471388534</v>
+        <v>1.122587054603432</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731432177027933</v>
+        <v>4.684646858211232</v>
       </c>
       <c r="K16" t="n">
-        <v>18.76986746038505</v>
+        <v>22.88135812343139</v>
       </c>
       <c r="L16" t="n">
-        <v>43.33990836315563</v>
+        <v>42.3297867772224</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92734382966947</v>
+        <v>99.96259857946012</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.77995873544714</v>
+        <v>82.5514864097148</v>
       </c>
       <c r="C17" t="n">
-        <v>38.93923260913024</v>
+        <v>38.34455322863366</v>
       </c>
       <c r="D17" t="n">
-        <v>1.435737825581697</v>
+        <v>1.369434759271932</v>
       </c>
       <c r="E17" t="n">
-        <v>12.71504821469787</v>
+        <v>11.93243707419069</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577035161229978</v>
+        <v>0.7499231498257949</v>
       </c>
       <c r="G17" t="n">
-        <v>24.06543044175243</v>
+        <v>24.31218020818909</v>
       </c>
       <c r="H17" t="n">
-        <v>36.85815969655263</v>
+        <v>38.24609284928493</v>
       </c>
       <c r="I17" t="n">
-        <v>2.212232064970773</v>
+        <v>1.254398682541154</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735646975768735</v>
+        <v>4.687019686411217</v>
       </c>
       <c r="K17" t="n">
-        <v>17.22004126455286</v>
+        <v>17.44851359028518</v>
       </c>
       <c r="L17" t="n">
-        <v>43.76705068817145</v>
+        <v>44.1651410598593</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92632456185456</v>
+        <v>99.95820787877815</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.52649432502717</v>
+        <v>84.2967000336462</v>
       </c>
       <c r="C18" t="n">
-        <v>37.0277100412032</v>
+        <v>39.09201208716971</v>
       </c>
       <c r="D18" t="n">
-        <v>1.352109660112898</v>
+        <v>1.370626204060542</v>
       </c>
       <c r="E18" t="n">
-        <v>12.28191731205259</v>
+        <v>12.5508327823418</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582821718219219</v>
+        <v>0.7505756029804037</v>
       </c>
       <c r="G18" t="n">
-        <v>22.66367883835969</v>
+        <v>24.45398859160665</v>
       </c>
       <c r="H18" t="n">
-        <v>36.88630815265245</v>
+        <v>38.27936797079141</v>
       </c>
       <c r="I18" t="n">
-        <v>1.844934616140615</v>
+        <v>2.20021136323787</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739263573887011</v>
+        <v>4.691097518627522</v>
       </c>
       <c r="K18" t="n">
-        <v>19.47350567497282</v>
+        <v>15.7032999663538</v>
       </c>
       <c r="L18" t="n">
-        <v>43.43733339313034</v>
+        <v>45.13141132032228</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93854910930636</v>
+        <v>99.92672337384579</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.63004086132536</v>
+        <v>81.48901940922484</v>
       </c>
       <c r="C19" t="n">
-        <v>36.41577543755368</v>
+        <v>36.62392746812885</v>
       </c>
       <c r="D19" t="n">
-        <v>1.319565515734798</v>
+        <v>1.271299923352669</v>
       </c>
       <c r="E19" t="n">
-        <v>12.24270780968883</v>
+        <v>11.94711567745793</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587705002168673</v>
+        <v>0.7511389592070051</v>
       </c>
       <c r="G19" t="n">
-        <v>22.11818311562898</v>
+        <v>22.68186156814741</v>
       </c>
       <c r="H19" t="n">
-        <v>36.91006267613329</v>
+        <v>38.30809914751909</v>
       </c>
       <c r="I19" t="n">
-        <v>1.538435617567158</v>
+        <v>1.834885638496952</v>
       </c>
       <c r="J19" t="n">
-        <v>4.74231562635542</v>
+        <v>4.694618495043781</v>
       </c>
       <c r="K19" t="n">
-        <v>20.36995913867467</v>
+        <v>18.51098059077516</v>
       </c>
       <c r="L19" t="n">
-        <v>43.16301723998997</v>
+        <v>44.80397495878383</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94875181621831</v>
+        <v>99.93888301768784</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.11267285052679</v>
+        <v>78.64912764262714</v>
       </c>
       <c r="C20" t="n">
-        <v>34.13553054402193</v>
+        <v>34.06636958913633</v>
       </c>
       <c r="D20" t="n">
-        <v>1.227146093753955</v>
+        <v>1.171492923949556</v>
       </c>
       <c r="E20" t="n">
-        <v>11.59904598587381</v>
+        <v>11.26418402880132</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7591912290255134</v>
+        <v>0.7516260550433753</v>
       </c>
       <c r="G20" t="n">
-        <v>20.56907496265138</v>
+        <v>20.9011578157052</v>
       </c>
       <c r="H20" t="n">
-        <v>36.93052884698777</v>
+        <v>38.33294104310351</v>
       </c>
       <c r="I20" t="n">
-        <v>1.282740550824891</v>
+        <v>1.530062932003074</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744945181409458</v>
+        <v>4.697662844021095</v>
       </c>
       <c r="K20" t="n">
-        <v>22.88732714947321</v>
+        <v>21.35087235737287</v>
       </c>
       <c r="L20" t="n">
-        <v>42.93440798379467</v>
+        <v>44.531789007977</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95726567728981</v>
+        <v>99.94903095448619</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.68218648158121</v>
+        <v>75.94542391756255</v>
       </c>
       <c r="C21" t="n">
-        <v>37.49334059770237</v>
+        <v>31.59726583899084</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2281070951551</v>
+        <v>1.077084585404673</v>
       </c>
       <c r="E21" t="n">
-        <v>13.44075292774687</v>
+        <v>10.56905305865443</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7597857660888213</v>
+        <v>0.7520469271304071</v>
       </c>
       <c r="G21" t="n">
-        <v>22.09405655547619</v>
+        <v>19.21677411802775</v>
       </c>
       <c r="H21" t="n">
-        <v>38.4683234049417</v>
+        <v>38.35440552639361</v>
       </c>
       <c r="I21" t="n">
-        <v>1.942499694117399</v>
+        <v>1.275766407386637</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748661038055132</v>
+        <v>4.700293294565044</v>
       </c>
       <c r="K21" t="n">
-        <v>17.3178135184188</v>
+        <v>24.05457608243746</v>
       </c>
       <c r="L21" t="n">
-        <v>45.12414656134258</v>
+        <v>44.3056563304605</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93530067746376</v>
+        <v>99.95749825188881</v>
       </c>
     </row>
   </sheetData>
